--- a/Result/profitability/8039.xlsx
+++ b/Result/profitability/8039.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.18</v>
       </c>
       <c r="M2" t="n">
-        <v>0.45625</v>
+        <v>0.48875</v>
       </c>
       <c r="N2" t="n">
-        <v>19.375</v>
+        <v>19.61125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.25</v>
       </c>
       <c r="M3" t="n">
-        <v>0.40625</v>
+        <v>0.50875</v>
       </c>
       <c r="N3" t="n">
-        <v>19.41625</v>
+        <v>20.3425</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>0.52</v>
+        <v>0.59375</v>
       </c>
       <c r="N4" t="n">
-        <v>20.66875</v>
+        <v>21.2175</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0.48125</v>
+        <v>0.57875</v>
       </c>
       <c r="N5" t="n">
-        <v>19.7125</v>
+        <v>20.095</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>0.17</v>
       </c>
       <c r="M6" t="n">
-        <v>0.48625</v>
+        <v>0.49</v>
       </c>
       <c r="N6" t="n">
-        <v>19.39</v>
+        <v>19.9675</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.59</v>
       </c>
       <c r="M7" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="N7" t="n">
-        <v>20.06625</v>
+        <v>20.51125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.92</v>
       </c>
       <c r="M8" t="n">
-        <v>0.47125</v>
+        <v>0.50375</v>
       </c>
       <c r="N8" t="n">
-        <v>20.61125</v>
+        <v>20.74875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -2026,7 +2026,7 @@
         <v>0.89</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8425000000000001</v>
+        <v>0.8425</v>
       </c>
       <c r="N13" t="n">
         <v>23.1225</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8039</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2696</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2073</v>
+      </c>
+      <c r="E75" t="n">
+        <v>624</v>
+      </c>
+      <c r="F75" t="n">
+        <v>23.13</v>
+      </c>
+      <c r="G75" t="n">
+        <v>173</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6.41%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>138</v>
+      </c>
+      <c r="J75" t="n">
+        <v>311</v>
+      </c>
+      <c r="K75" t="n">
+        <v>240</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.5475</v>
+      </c>
+      <c r="N75" t="n">
+        <v>19.87625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.099999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.04993191103041306</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.059999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1524663677130045</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
